--- a/2026-ECMFA/RQ1/results/experiment_run_gpt-4_o-mini.xlsx
+++ b/2026-ECMFA/RQ1/results/experiment_run_gpt-4_o-mini.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\proyectos\emf-kaizen-experiments\2026-ECMFA\results\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\proyectos\emf-kaizen-experiments\2026-ECMFA\RQ1\results\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{186D7138-33B1-4AD2-89F3-A6F2C7CB6EB0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FE37DBC8-378D-438F-9C06-21553D361D56}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="eval run syntax" sheetId="3" r:id="rId1"/>
@@ -60,7 +60,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="484" uniqueCount="78">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="482" uniqueCount="76">
   <si>
     <t>Meta-models</t>
   </si>
@@ -191,15 +191,6 @@
     <t>Missing reference</t>
   </si>
   <si>
-    <t>No response</t>
-  </si>
-  <si>
-    <t>Response shown as text in chat</t>
-  </si>
-  <si>
-    <t>Other errors</t>
-  </si>
-  <si>
     <t>Has some elements repeated from the current model, unnecesarily</t>
   </si>
   <si>
@@ -294,6 +285,9 @@
   </si>
   <si>
     <t>gpt-4o-mini</t>
+  </si>
+  <si>
+    <t>Incorrect intent</t>
   </si>
 </sst>
 </file>
@@ -1496,7 +1490,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:S27"/>
+  <dimension ref="A1:Q25"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="10.90625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="14" bestFit="1" customWidth="1"/>
@@ -1505,16 +1499,16 @@
     <col min="4" max="11" width="11.26953125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>38</v>
       </c>
       <c r="B1" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="2" spans="1:19" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
-    <row r="3" spans="1:19" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="2" spans="1:17" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
+    <row r="3" spans="1:17" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="D3" s="72" t="s">
         <v>8</v>
       </c>
@@ -1532,7 +1526,7 @@
       </c>
       <c r="K3" s="75"/>
     </row>
-    <row r="4" spans="1:19" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:17" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A4" s="3" t="s">
         <v>0</v>
       </c>
@@ -1578,17 +1572,11 @@
       <c r="P4">
         <v>4</v>
       </c>
-      <c r="Q4">
-        <v>5</v>
-      </c>
-      <c r="R4">
-        <v>6</v>
-      </c>
-      <c r="S4" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="5" spans="1:19" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="Q4" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="5" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="69" t="s">
         <v>1</v>
       </c>
@@ -1605,7 +1593,7 @@
         <v>1</v>
       </c>
       <c r="F5" s="5">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G5" s="5">
         <v>1</v>
@@ -1623,14 +1611,14 @@
         <v>1</v>
       </c>
       <c r="L5" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="M5">
         <f>COUNTIF($D5:$K7,M4)</f>
         <v>19</v>
       </c>
       <c r="N5">
-        <f t="shared" ref="N5:R5" si="0">COUNTIF($D5:$K7,N4)</f>
+        <f t="shared" ref="N5:P5" si="0">COUNTIF($D5:$K7,N4)</f>
         <v>0</v>
       </c>
       <c r="O5">
@@ -1639,22 +1627,14 @@
       </c>
       <c r="P5">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Q5">
-        <f t="shared" si="0"/>
-        <v>3</v>
-      </c>
-      <c r="R5">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="S5">
-        <f>SUM(M5:R5)</f>
+        <f>SUM(M5:P5)</f>
         <v>24</v>
       </c>
     </row>
-    <row r="6" spans="1:19" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="70"/>
       <c r="B6" s="6" t="s">
         <v>3</v>
@@ -1669,7 +1649,7 @@
         <v>1</v>
       </c>
       <c r="F6" s="6">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G6" s="6">
         <v>1</v>
@@ -1687,14 +1667,14 @@
         <v>3</v>
       </c>
       <c r="L6" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="M6">
         <f>100*M5/24</f>
         <v>79.166666666666671</v>
       </c>
       <c r="N6">
-        <f t="shared" ref="N6:R6" si="1">100*N5/24</f>
+        <f t="shared" ref="N6:P6" si="1">100*N5/24</f>
         <v>0</v>
       </c>
       <c r="O6">
@@ -1703,18 +1683,10 @@
       </c>
       <c r="P6">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="Q6">
-        <f t="shared" si="1"/>
         <v>12.5</v>
       </c>
-      <c r="R6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:19" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    </row>
+    <row r="7" spans="1:17" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A7" s="71"/>
       <c r="B7" s="7" t="s">
         <v>4</v>
@@ -1729,7 +1701,7 @@
         <v>1</v>
       </c>
       <c r="F7" s="7">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G7" s="7">
         <v>1</v>
@@ -1747,7 +1719,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:19" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="76" t="s">
         <v>20</v>
       </c>
@@ -1764,7 +1736,7 @@
         <v>1</v>
       </c>
       <c r="F8" s="5">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G8" s="5">
         <v>1</v>
@@ -1782,14 +1754,14 @@
         <v>1</v>
       </c>
       <c r="L8" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="M8">
         <f>COUNTIF($D8:$K10,M4)</f>
         <v>23</v>
       </c>
       <c r="N8">
-        <f t="shared" ref="N8:R8" si="2">COUNTIF($D8:$K10,N4)</f>
+        <f t="shared" ref="N8:P8" si="2">COUNTIF($D8:$K10,N4)</f>
         <v>0</v>
       </c>
       <c r="O8">
@@ -1798,22 +1770,14 @@
       </c>
       <c r="P8">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q8">
-        <f t="shared" si="2"/>
-        <v>1</v>
-      </c>
-      <c r="R8">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="S8">
-        <f>SUM(M8:R8)</f>
+        <f>SUM(M8:P8)</f>
         <v>24</v>
       </c>
     </row>
-    <row r="9" spans="1:19" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A9" s="77"/>
       <c r="B9" s="6" t="s">
         <v>3</v>
@@ -1846,14 +1810,14 @@
         <v>1</v>
       </c>
       <c r="L9" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="M9">
         <f>100*M8/24</f>
         <v>95.833333333333329</v>
       </c>
       <c r="N9">
-        <f t="shared" ref="N9:R9" si="3">100*N8/24</f>
+        <f t="shared" ref="N9:P9" si="3">100*N8/24</f>
         <v>0</v>
       </c>
       <c r="O9">
@@ -1862,18 +1826,10 @@
       </c>
       <c r="P9">
         <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="Q9">
-        <f t="shared" si="3"/>
         <v>4.166666666666667</v>
       </c>
-      <c r="R9">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="1:19" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    </row>
+    <row r="10" spans="1:17" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A10" s="78"/>
       <c r="B10" s="7" t="s">
         <v>4</v>
@@ -1906,7 +1862,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:19" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A11" s="69" t="s">
         <v>2</v>
       </c>
@@ -1923,7 +1879,7 @@
         <v>1</v>
       </c>
       <c r="F11" s="6">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G11" s="6">
         <v>1</v>
@@ -1941,14 +1897,14 @@
         <v>1</v>
       </c>
       <c r="L11" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="M11">
         <f>COUNTIF($D11:$K13,M4)</f>
         <v>21</v>
       </c>
       <c r="N11">
-        <f t="shared" ref="N11:R11" si="4">COUNTIF($D11:$K13,N4)</f>
+        <f t="shared" ref="N11:P11" si="4">COUNTIF($D11:$K13,N4)</f>
         <v>0</v>
       </c>
       <c r="O11">
@@ -1957,22 +1913,14 @@
       </c>
       <c r="P11">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Q11">
-        <f t="shared" si="4"/>
-        <v>3</v>
-      </c>
-      <c r="R11">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="S11">
-        <f>SUM(M11:R11)</f>
+        <f>SUM(M11:P11)</f>
         <v>24</v>
       </c>
     </row>
-    <row r="12" spans="1:19" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A12" s="70"/>
       <c r="B12" s="6" t="s">
         <v>3</v>
@@ -1987,7 +1935,7 @@
         <v>1</v>
       </c>
       <c r="F12" s="6">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G12" s="6">
         <v>1</v>
@@ -2005,14 +1953,14 @@
         <v>1</v>
       </c>
       <c r="L12" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="M12">
         <f>100*M11/24</f>
         <v>87.5</v>
       </c>
       <c r="N12">
-        <f t="shared" ref="N12:R12" si="5">100*N11/24</f>
+        <f t="shared" ref="N12:P12" si="5">100*N11/24</f>
         <v>0</v>
       </c>
       <c r="O12">
@@ -2021,18 +1969,10 @@
       </c>
       <c r="P12">
         <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="Q12">
-        <f t="shared" si="5"/>
         <v>12.5</v>
       </c>
-      <c r="R12">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" spans="1:19" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    </row>
+    <row r="13" spans="1:17" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A13" s="71"/>
       <c r="B13" s="7" t="s">
         <v>4</v>
@@ -2047,7 +1987,7 @@
         <v>1</v>
       </c>
       <c r="F13" s="19">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G13" s="19">
         <v>1</v>
@@ -2065,7 +2005,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="14" spans="1:19" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A14" s="69" t="s">
         <v>17</v>
       </c>
@@ -2082,7 +2022,7 @@
         <v>1</v>
       </c>
       <c r="F14" s="5">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G14" s="5">
         <v>1</v>
@@ -2100,14 +2040,14 @@
         <v>1</v>
       </c>
       <c r="L14" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="M14">
         <f>COUNTIF($D14:$K16,M4)</f>
         <v>21</v>
       </c>
       <c r="N14">
-        <f t="shared" ref="N14:R14" si="6">COUNTIF($D14:$K16,N4)</f>
+        <f t="shared" ref="N14:P14" si="6">COUNTIF($D14:$K16,N4)</f>
         <v>0</v>
       </c>
       <c r="O14">
@@ -2116,22 +2056,14 @@
       </c>
       <c r="P14">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Q14">
-        <f t="shared" si="6"/>
-        <v>3</v>
-      </c>
-      <c r="R14">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="S14">
-        <f>SUM(M14:R14)</f>
+        <f>SUM(M14:P14)</f>
         <v>24</v>
       </c>
     </row>
-    <row r="15" spans="1:19" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A15" s="70"/>
       <c r="B15" s="6" t="s">
         <v>3</v>
@@ -2146,7 +2078,7 @@
         <v>1</v>
       </c>
       <c r="F15" s="6">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G15" s="6">
         <v>1</v>
@@ -2164,14 +2096,14 @@
         <v>1</v>
       </c>
       <c r="L15" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="M15">
         <f>100*M14/24</f>
         <v>87.5</v>
       </c>
       <c r="N15">
-        <f t="shared" ref="N15:R15" si="7">100*N14/24</f>
+        <f t="shared" ref="N15:P15" si="7">100*N14/24</f>
         <v>0</v>
       </c>
       <c r="O15">
@@ -2180,18 +2112,10 @@
       </c>
       <c r="P15">
         <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="Q15">
-        <f t="shared" si="7"/>
         <v>12.5</v>
       </c>
-      <c r="R15">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16" spans="1:19" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    </row>
+    <row r="16" spans="1:17" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A16" s="71"/>
       <c r="B16" s="7" t="s">
         <v>4</v>
@@ -2206,7 +2130,7 @@
         <v>1</v>
       </c>
       <c r="F16" s="7">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G16" s="7">
         <v>1</v>
@@ -2224,7 +2148,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="17" spans="1:19" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A17" s="69" t="s">
         <v>19</v>
       </c>
@@ -2241,7 +2165,7 @@
         <v>1</v>
       </c>
       <c r="F17" s="20">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G17" s="20">
         <v>1</v>
@@ -2259,14 +2183,14 @@
         <v>3</v>
       </c>
       <c r="L17" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="M17">
         <f>COUNTIF($D17:$K19,M4)</f>
         <v>17</v>
       </c>
       <c r="N17">
-        <f t="shared" ref="N17:R17" si="8">COUNTIF($D17:$K19,N4)</f>
+        <f t="shared" ref="N17:P17" si="8">COUNTIF($D17:$K19,N4)</f>
         <v>0</v>
       </c>
       <c r="O17">
@@ -2275,22 +2199,14 @@
       </c>
       <c r="P17">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="Q17">
-        <f t="shared" si="8"/>
-        <v>4</v>
-      </c>
-      <c r="R17">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="S17">
-        <f>SUM(M17:R17)</f>
+        <f>SUM(M17:P17)</f>
         <v>24</v>
       </c>
     </row>
-    <row r="18" spans="1:19" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A18" s="70"/>
       <c r="B18" s="6" t="s">
         <v>3</v>
@@ -2305,10 +2221,10 @@
         <v>1</v>
       </c>
       <c r="F18" s="6">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G18" s="6">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H18" s="6">
         <v>1</v>
@@ -2323,14 +2239,14 @@
         <v>3</v>
       </c>
       <c r="L18" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="M18">
         <f>100*M17/24</f>
         <v>70.833333333333329</v>
       </c>
       <c r="N18">
-        <f t="shared" ref="N18:R18" si="9">100*N17/24</f>
+        <f t="shared" ref="N18:P18" si="9">100*N17/24</f>
         <v>0</v>
       </c>
       <c r="O18">
@@ -2339,18 +2255,10 @@
       </c>
       <c r="P18">
         <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="Q18">
-        <f t="shared" si="9"/>
         <v>16.666666666666668</v>
       </c>
-      <c r="R18">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19" spans="1:19" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    </row>
+    <row r="19" spans="1:17" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A19" s="71"/>
       <c r="B19" s="7" t="s">
         <v>4</v>
@@ -2365,7 +2273,7 @@
         <v>1</v>
       </c>
       <c r="F19" s="7">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G19" s="7">
         <v>1</v>
@@ -2383,15 +2291,15 @@
         <v>1</v>
       </c>
     </row>
-    <row r="21" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:17" x14ac:dyDescent="0.35">
       <c r="E21" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="F21" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="22" spans="1:19" x14ac:dyDescent="0.35">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="22" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
         <v>39</v>
       </c>
@@ -2410,7 +2318,7 @@
         <v>84.166666666666671</v>
       </c>
     </row>
-    <row r="23" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:17" x14ac:dyDescent="0.35">
       <c r="B23">
         <v>2</v>
       </c>
@@ -2418,15 +2326,15 @@
         <v>41</v>
       </c>
       <c r="E23">
-        <f t="shared" ref="E23:E27" si="10">COUNTIF(D$5:K$19,B23)</f>
+        <f t="shared" ref="E23:E25" si="10">COUNTIF(D$5:K$19,B23)</f>
         <v>0</v>
       </c>
       <c r="F23">
-        <f t="shared" ref="F23:F27" si="11">100*E23/(15*8)</f>
+        <f t="shared" ref="F23:F25" si="11">100*E23/(15*8)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:17" x14ac:dyDescent="0.35">
       <c r="B24">
         <v>3</v>
       </c>
@@ -2442,52 +2350,20 @@
         <v>4.166666666666667</v>
       </c>
     </row>
-    <row r="25" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:17" x14ac:dyDescent="0.35">
       <c r="B25">
         <v>4</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>43</v>
+        <v>75</v>
       </c>
       <c r="E25">
         <f t="shared" si="10"/>
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="F25">
         <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="26" spans="1:19" x14ac:dyDescent="0.35">
-      <c r="B26">
-        <v>5</v>
-      </c>
-      <c r="C26" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="E26">
-        <f t="shared" si="10"/>
-        <v>14</v>
-      </c>
-      <c r="F26">
-        <f t="shared" si="11"/>
         <v>11.666666666666666</v>
-      </c>
-    </row>
-    <row r="27" spans="1:19" x14ac:dyDescent="0.35">
-      <c r="B27">
-        <v>6</v>
-      </c>
-      <c r="C27" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="E27">
-        <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-      <c r="F27">
-        <f t="shared" si="11"/>
-        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -2524,7 +2400,7 @@
         <v>38</v>
       </c>
       <c r="B1" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
     </row>
     <row r="2" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
@@ -2581,10 +2457,10 @@
         <v>16</v>
       </c>
       <c r="N4" s="29" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="O4" s="29" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
     </row>
     <row r="5" spans="1:15" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
@@ -2604,7 +2480,7 @@
         <v>1</v>
       </c>
       <c r="F5" s="30" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="G5" s="5">
         <v>1</v>
@@ -2651,7 +2527,7 @@
         <v>1</v>
       </c>
       <c r="F6" s="33" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="G6" s="6">
         <v>1</v>
@@ -2672,7 +2548,7 @@
         <v>2</v>
       </c>
       <c r="M6" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="N6">
         <f t="shared" ref="N6:N7" si="0">COUNTIF(D$5:K$7,L6)</f>
@@ -2698,7 +2574,7 @@
         <v>1</v>
       </c>
       <c r="F7" s="34" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="G7" s="7">
         <v>1</v>
@@ -2719,7 +2595,7 @@
         <v>3</v>
       </c>
       <c r="M7" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="N7">
         <f t="shared" si="0"/>
@@ -2747,7 +2623,7 @@
         <v>1</v>
       </c>
       <c r="F8" s="30" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="G8" s="5">
         <v>1</v>
@@ -2815,7 +2691,7 @@
         <v>2</v>
       </c>
       <c r="M9" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="N9">
         <f t="shared" ref="N9:N10" si="2">COUNTIF(D$8:K$10,L9)</f>
@@ -2862,7 +2738,7 @@
         <v>3</v>
       </c>
       <c r="M10" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="N10">
         <f t="shared" si="2"/>
@@ -2890,7 +2766,7 @@
         <v>1</v>
       </c>
       <c r="F11" s="33" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="G11" s="6">
         <v>1</v>
@@ -2937,7 +2813,7 @@
         <v>1</v>
       </c>
       <c r="F12" s="33" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="G12" s="6">
         <v>1</v>
@@ -2958,7 +2834,7 @@
         <v>2</v>
       </c>
       <c r="M12" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="N12">
         <f t="shared" ref="N12:N13" si="4">COUNTIF(D$11:K$13,L12)</f>
@@ -2984,7 +2860,7 @@
         <v>1</v>
       </c>
       <c r="F13" s="45" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="G13" s="19">
         <v>2</v>
@@ -3005,7 +2881,7 @@
         <v>3</v>
       </c>
       <c r="M13" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="N13">
         <f t="shared" si="4"/>
@@ -3033,7 +2909,7 @@
         <v>1</v>
       </c>
       <c r="F14" s="30" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="G14" s="5">
         <v>1</v>
@@ -3080,7 +2956,7 @@
         <v>1</v>
       </c>
       <c r="F15" s="33" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="G15" s="6">
         <v>1</v>
@@ -3101,7 +2977,7 @@
         <v>2</v>
       </c>
       <c r="M15" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="N15">
         <f t="shared" ref="N15:N16" si="6">COUNTIF(D$14:K$16,L15)</f>
@@ -3127,7 +3003,7 @@
         <v>1</v>
       </c>
       <c r="F16" s="34" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="G16" s="7">
         <v>1</v>
@@ -3148,7 +3024,7 @@
         <v>3</v>
       </c>
       <c r="M16" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="N16">
         <f t="shared" si="6"/>
@@ -3176,7 +3052,7 @@
         <v>1</v>
       </c>
       <c r="F17" s="46" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="G17" s="20">
         <v>2</v>
@@ -3223,10 +3099,10 @@
         <v>1</v>
       </c>
       <c r="F18" s="33" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="G18" s="33" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="H18" s="6">
         <v>1</v>
@@ -3244,7 +3120,7 @@
         <v>2</v>
       </c>
       <c r="M18" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="N18">
         <f t="shared" ref="N18:N19" si="7">COUNTIF(D$17:K$19,L18)</f>
@@ -3270,7 +3146,7 @@
         <v>1</v>
       </c>
       <c r="F19" s="34" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="G19" s="7">
         <v>1</v>
@@ -3291,7 +3167,7 @@
         <v>3</v>
       </c>
       <c r="M19" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="N19">
         <f t="shared" si="7"/>
@@ -3304,10 +3180,10 @@
     </row>
     <row r="21" spans="1:15" x14ac:dyDescent="0.35">
       <c r="F21" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="G21" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
     </row>
     <row r="22" spans="1:15" x14ac:dyDescent="0.35">
@@ -3334,7 +3210,7 @@
         <v>2</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="F23">
         <f>COUNTIF(D$5:K$19,B23)</f>
@@ -3350,7 +3226,7 @@
         <v>3</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="F24">
         <f>COUNTIF(D$5:K$19,B24)</f>
@@ -3394,12 +3270,12 @@
         <v>38</v>
       </c>
       <c r="B1" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
     </row>
     <row r="2" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A2" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
     </row>
     <row r="3" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -3455,10 +3331,10 @@
         <v>16</v>
       </c>
       <c r="N4" s="29" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="O4" s="29" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
     </row>
     <row r="5" spans="1:15" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
@@ -3499,7 +3375,7 @@
         <v>1</v>
       </c>
       <c r="M5" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="N5">
         <f>COUNTIF(D$5:K$7,L5)</f>
@@ -3546,7 +3422,7 @@
         <v>2</v>
       </c>
       <c r="M6" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="N6">
         <f t="shared" ref="N6:N7" si="0">COUNTIF(D$5:K$7,L6)</f>
@@ -3593,7 +3469,7 @@
         <v>3</v>
       </c>
       <c r="M7" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="N7">
         <f t="shared" si="0"/>
@@ -3642,7 +3518,7 @@
         <v>1</v>
       </c>
       <c r="M8" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="N8">
         <f>COUNTIF(D$8:K$10,L8)</f>
@@ -3689,7 +3565,7 @@
         <v>2</v>
       </c>
       <c r="M9" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="N9">
         <f t="shared" ref="N9:N10" si="2">COUNTIF(D$8:K$10,L9)</f>
@@ -3736,7 +3612,7 @@
         <v>3</v>
       </c>
       <c r="M10" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="N10">
         <f t="shared" si="2"/>
@@ -3785,7 +3661,7 @@
         <v>1</v>
       </c>
       <c r="M11" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="N11">
         <f>COUNTIF(D$11:K$13,L11)</f>
@@ -3832,7 +3708,7 @@
         <v>2</v>
       </c>
       <c r="M12" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="N12">
         <f t="shared" ref="N12:N13" si="3">COUNTIF(D$11:K$13,L12)</f>
@@ -3879,7 +3755,7 @@
         <v>3</v>
       </c>
       <c r="M13" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="N13">
         <f t="shared" si="3"/>
@@ -3928,7 +3804,7 @@
         <v>1</v>
       </c>
       <c r="M14" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="N14">
         <f>COUNTIF(D$14:K$16,L14)</f>
@@ -3975,7 +3851,7 @@
         <v>2</v>
       </c>
       <c r="M15" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="N15">
         <f t="shared" ref="N15:N16" si="4">COUNTIF(D$14:K$16,L15)</f>
@@ -4022,7 +3898,7 @@
         <v>3</v>
       </c>
       <c r="M16" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="N16">
         <f t="shared" si="4"/>
@@ -4071,7 +3947,7 @@
         <v>1</v>
       </c>
       <c r="M17" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="N17">
         <f>COUNTIF(D$17:K$19,L17)</f>
@@ -4118,7 +3994,7 @@
         <v>2</v>
       </c>
       <c r="M18" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="N18">
         <f t="shared" ref="N18:N19" si="5">COUNTIF(D$17:K$19,L18)</f>
@@ -4165,7 +4041,7 @@
         <v>3</v>
       </c>
       <c r="M19" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="N19">
         <f t="shared" si="5"/>
@@ -4178,10 +4054,10 @@
     </row>
     <row r="21" spans="1:15" x14ac:dyDescent="0.35">
       <c r="D21" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="E21" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
     </row>
     <row r="22" spans="1:15" x14ac:dyDescent="0.35">
@@ -4192,7 +4068,7 @@
         <v>1</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="D22">
         <f>COUNTIF(D$5:K$19,B22)</f>
@@ -4208,7 +4084,7 @@
         <v>2</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="D23">
         <f t="shared" ref="D23:D24" si="6">COUNTIF(D$5:K$19,B23)</f>
@@ -4224,7 +4100,7 @@
         <v>3</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="D24">
         <f t="shared" si="6"/>
@@ -4267,7 +4143,7 @@
         <v>38</v>
       </c>
       <c r="B1" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
     </row>
     <row r="2" spans="1:16" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
@@ -4289,7 +4165,7 @@
       </c>
       <c r="K3" s="75"/>
       <c r="M3" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
     </row>
     <row r="4" spans="1:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -4330,13 +4206,13 @@
         <v>8</v>
       </c>
       <c r="N4" s="47" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="O4" s="47" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="P4" s="47" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
     </row>
     <row r="5" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
@@ -4532,7 +4408,7 @@
         <v>3</v>
       </c>
       <c r="L8" s="1" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="M8">
         <f>SUM(M5:M7)</f>
@@ -4933,10 +4809,10 @@
     </row>
     <row r="21" spans="1:12" x14ac:dyDescent="0.35">
       <c r="D21" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="E21" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
     </row>
     <row r="22" spans="1:12" x14ac:dyDescent="0.35">
@@ -4947,7 +4823,7 @@
         <v>1</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="D22">
         <f>COUNTIF(D$5:K$19,B22)</f>
@@ -4963,7 +4839,7 @@
         <v>2</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="D23">
         <f t="shared" ref="D23:D24" si="4">COUNTIF(D$5:K$19,B23)</f>
@@ -4979,7 +4855,7 @@
         <v>3</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="D24">
         <f t="shared" si="4"/>
@@ -5022,7 +4898,7 @@
         <v>38</v>
       </c>
       <c r="B1" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
     </row>
     <row r="2" spans="1:16" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
@@ -5044,7 +4920,7 @@
       </c>
       <c r="K3" s="75"/>
       <c r="M3" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
     </row>
     <row r="4" spans="1:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -5082,16 +4958,16 @@
         <v>16</v>
       </c>
       <c r="M4" s="48" t="s">
+        <v>68</v>
+      </c>
+      <c r="N4" s="48" t="s">
+        <v>69</v>
+      </c>
+      <c r="O4" s="48" t="s">
+        <v>70</v>
+      </c>
+      <c r="P4" s="48" t="s">
         <v>71</v>
-      </c>
-      <c r="N4" s="48" t="s">
-        <v>72</v>
-      </c>
-      <c r="O4" s="48" t="s">
-        <v>73</v>
-      </c>
-      <c r="P4" s="48" t="s">
-        <v>74</v>
       </c>
     </row>
     <row r="5" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
@@ -5699,7 +5575,7 @@
     </row>
     <row r="21" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="B21">
         <f>SUM(D5:K19)/120</f>
@@ -5708,7 +5584,7 @@
     </row>
     <row r="22" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="B22">
         <f>MIN(D5:K19)</f>
@@ -5717,7 +5593,7 @@
     </row>
     <row r="23" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="B23">
         <f>MAX(D5:K19)</f>
@@ -5726,7 +5602,6 @@
     </row>
   </sheetData>
   <mergeCells count="9">
-    <mergeCell ref="A14:A16"/>
     <mergeCell ref="A17:A19"/>
     <mergeCell ref="D3:E3"/>
     <mergeCell ref="F3:G3"/>
@@ -5735,6 +5610,7 @@
     <mergeCell ref="A5:A7"/>
     <mergeCell ref="A8:A10"/>
     <mergeCell ref="A11:A13"/>
+    <mergeCell ref="A14:A16"/>
   </mergeCells>
   <conditionalFormatting sqref="D5:K19">
     <cfRule type="colorScale" priority="1">
@@ -5768,7 +5644,7 @@
         <v>38</v>
       </c>
       <c r="B1" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
     </row>
     <row r="2" spans="1:16" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
@@ -5790,7 +5666,7 @@
       </c>
       <c r="K3" s="75"/>
       <c r="M3" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
     </row>
     <row r="4" spans="1:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -5828,16 +5704,16 @@
         <v>16</v>
       </c>
       <c r="M4" s="48" t="s">
+        <v>68</v>
+      </c>
+      <c r="N4" s="48" t="s">
+        <v>69</v>
+      </c>
+      <c r="O4" s="48" t="s">
+        <v>70</v>
+      </c>
+      <c r="P4" s="48" t="s">
         <v>71</v>
-      </c>
-      <c r="N4" s="48" t="s">
-        <v>72</v>
-      </c>
-      <c r="O4" s="48" t="s">
-        <v>73</v>
-      </c>
-      <c r="P4" s="48" t="s">
-        <v>74</v>
       </c>
     </row>
     <row r="5" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
@@ -6445,7 +6321,7 @@
     </row>
     <row r="21" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="B21">
         <f>SUM(D5:K19)/120</f>
@@ -6454,7 +6330,7 @@
     </row>
     <row r="22" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="B22">
         <f>MIN(D5:K19)</f>
@@ -6463,7 +6339,7 @@
     </row>
     <row r="23" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="B23">
         <f>MAX(D5:K19)</f>
@@ -6514,7 +6390,7 @@
         <v>38</v>
       </c>
       <c r="B1" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
     </row>
     <row r="2" spans="1:16" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
@@ -6536,7 +6412,7 @@
       </c>
       <c r="K3" s="82"/>
       <c r="M3" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
     </row>
     <row r="4" spans="1:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -6574,16 +6450,16 @@
         <v>16</v>
       </c>
       <c r="M4" s="48" t="s">
+        <v>68</v>
+      </c>
+      <c r="N4" s="48" t="s">
+        <v>69</v>
+      </c>
+      <c r="O4" s="48" t="s">
+        <v>70</v>
+      </c>
+      <c r="P4" s="48" t="s">
         <v>71</v>
-      </c>
-      <c r="N4" s="48" t="s">
-        <v>72</v>
-      </c>
-      <c r="O4" s="48" t="s">
-        <v>73</v>
-      </c>
-      <c r="P4" s="48" t="s">
-        <v>74</v>
       </c>
     </row>
     <row r="5" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
@@ -7191,7 +7067,7 @@
     </row>
     <row r="21" spans="1:16" x14ac:dyDescent="0.35">
       <c r="L21" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="M21">
         <f>MEDIAN(D5:E19)</f>
@@ -7215,10 +7091,10 @@
         <v>39</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="E22" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="F22" s="49">
         <f>MEDIAN(D5:K19)</f>
@@ -7227,7 +7103,7 @@
     </row>
     <row r="23" spans="1:16" x14ac:dyDescent="0.35">
       <c r="E23" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="F23" s="49">
         <f>MIN(D5:K19)</f>
@@ -7236,7 +7112,7 @@
     </row>
     <row r="24" spans="1:16" x14ac:dyDescent="0.35">
       <c r="E24" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="F24" s="49">
         <f>MAX(D5:K19)</f>
